--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -7172,7 +7172,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -7172,7 +7172,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251102_201330.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
